--- a/ngn-earnings-kit/references/scoring_matrix.xlsx
+++ b/ngn-earnings-kit/references/scoring_matrix.xlsx
@@ -34,7 +34,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +45,16 @@
       <patternFill patternType="solid">
         <fgColor rgb="00305496"/>
         <bgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -60,10 +70,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,7 +441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -453,165 +465,2388 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>Platform</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>NGN/h</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>Reliability</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>NG Access</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Entry Barrier</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Scalability</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Time-to-NGN</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Source URLs</t>
         </is>
       </c>
+      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>WEIGHTS</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Mercor</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>24000</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Wise/bank weekly; top pick</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Mercor</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C5" t="n">
-        <v>8</v>
-      </c>
-      <c r="D5" t="n">
-        <v>9</v>
-      </c>
-      <c r="E5" t="n">
-        <v>7</v>
-      </c>
-      <c r="F5" t="n">
-        <v>6</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7</v>
-      </c>
-      <c r="I5" t="n">
-        <v>8</v>
-      </c>
-      <c r="K5" t="n">
-        <v>15.6</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+          <t>DataAnnotation.tech</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>PayPal ~3-7d; steady</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DataAnnotation.tech</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7</v>
-      </c>
-      <c r="D6" t="n">
-        <v>8</v>
-      </c>
-      <c r="E6" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" t="n">
-        <v>5</v>
-      </c>
-      <c r="G6" t="n">
-        <v>6</v>
-      </c>
-      <c r="H6" t="n">
-        <v>6</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7</v>
-      </c>
-      <c r="K6" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+          <t>Invisible Technologies</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>35000</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>PayPal/Payoneer 2x/mo</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Stellar AI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>37500</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>7.45</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>PayPal weekly; $25 base</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NOTE: Rate each dimension 1-10 for each platform, total = SUMPRODUCT(weights, scores). Range below auto-scales.</t>
+          <t>Braintrust</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>net30 slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Micro1</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>45000</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>7.05</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>AI trainer $20-60</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Testlio</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hourly; weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>uTest (Applause)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>best NG crowdtesting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Respondent.io</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>60000</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>high value; low volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PlaybookUX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>30000</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>invite-only</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Remotasks/Outlier</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>6.35</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>weekly baseline</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Test.io</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>bug pace</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Betakitesting</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>22500</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Tremendous rails</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Userlytics</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>PayPal gate</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TimeBucks</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>$3 min; multi rails</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Mindrift (Toloka)</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>12000</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>bi-weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FreeCash</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>offer walls &gt; surveys</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Clickworker</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>weekly PayPal/Payoneer</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>CrowdGen (Appen)</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ai-training</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>10500</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SagaPoll</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>native NGN bank</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TGM Panel (NG)</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>good comp; PayPal gripes</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Premise</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>location tasks</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Trymata</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>9000</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Microworkers</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>$9 min</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>IntelliZoom</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>filler</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>PlaytestCloud</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>7500</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>low NG volume</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>UserFeel</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Toluna</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>huge NG panel; slow</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>UserDirect</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Ipsos iSay</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NG rate unverified</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Surveoo</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1500</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>KEEP</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NG redemption issues</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>GeoPoll</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>airtime not cash</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>UserTesting</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>NOT supported NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>UserInterviews</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>NOT supported NG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>Maze</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>user-testing</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>tool not panel</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Swagbucks</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>geo-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>Qmee</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>geo-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Prolific</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>geo-locked</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>MoBrog</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>surveys</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>ELIMINATED</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>VPN fraud risk</t>
         </is>
       </c>
     </row>

--- a/ngn-earnings-kit/references/scoring_matrix.xlsx
+++ b/ngn-earnings-kit/references/scoring_matrix.xlsx
@@ -445,7 +445,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -526,12 +526,12 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Field Agent</t>
+          <t>Telegram tap-to-earn</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>mystery-shopping</t>
+          <t>passive-apps</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
@@ -539,22 +539,22 @@
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="L4" s="4" t="inlineStr">
         <is>
-          <t>NG not served; SA only in Africa</t>
+          <t>Near-zero after TGE</t>
         </is>
       </c>
     </row>
